--- a/artfynd/A 60732-2025 artfynd.xlsx
+++ b/artfynd/A 60732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135070807</v>
+        <v>135070805</v>
       </c>
       <c r="B2" t="n">
-        <v>92406</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,21 +709,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834954</v>
+        <v>834914</v>
       </c>
       <c r="R2" t="n">
-        <v>7294841</v>
+        <v>7294883</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,21 +760,20 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På låga av gammal klen gran.</t>
+          <t>På en låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,53 +792,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135070805</v>
+        <v>134939129</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834914</v>
+        <v>835006</v>
       </c>
       <c r="R3" t="n">
-        <v>7294883</v>
+        <v>7294955</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,27 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en låga</t>
+          <t>På lutande halvt fallen gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,14 +899,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Andersson, AK Gustavsson, Mats Williamson</t>
+          <t>Lars Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134939129</v>
+        <v>134939130</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -942,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -958,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>835006</v>
+        <v>835017</v>
       </c>
       <c r="R4" t="n">
-        <v>7294955</v>
+        <v>7294977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lutande halvt fallen gammal gran.</t>
+          <t>På en klen död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134939130</v>
+        <v>134939131</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1056,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>835017</v>
+        <v>835012</v>
       </c>
       <c r="R5" t="n">
-        <v>7294977</v>
+        <v>7295013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en klen död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134939131</v>
+        <v>135070797</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1170,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1178,21 +1167,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>835012</v>
+        <v>834919</v>
       </c>
       <c r="R6" t="n">
-        <v>7295013</v>
+        <v>7295004</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,12 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1227,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,14 +1238,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Andersson</t>
+          <t>Lars Andersson, AK Gustavsson, Mats Williamson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135070797</v>
+        <v>135070802</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1279,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1287,16 +1283,18 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834919</v>
+        <v>834916</v>
       </c>
       <c r="R7" t="n">
-        <v>7295004</v>
+        <v>7294952</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1363,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135070802</v>
+        <v>135070803</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1395,7 +1393,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,18 +1401,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>834916</v>
+        <v>834917</v>
       </c>
       <c r="R8" t="n">
-        <v>7294952</v>
+        <v>7294926</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135070803</v>
+        <v>135070808</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1521,16 +1517,18 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>834917</v>
+        <v>834966</v>
       </c>
       <c r="R9" t="n">
-        <v>7294926</v>
+        <v>7294729</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1570,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grov gammal björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1602,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135070808</v>
+        <v>135070810</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1627,28 +1630,22 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>bålar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>834966</v>
+        <v>834980</v>
       </c>
       <c r="R10" t="n">
-        <v>7294729</v>
+        <v>7294906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På grov gammal björk</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135070810</v>
+        <v>135070811</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1750,7 +1742,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>bålar</t>
@@ -1762,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>834980</v>
+        <v>834975</v>
       </c>
       <c r="R11" t="n">
-        <v>7294906</v>
+        <v>7294913</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135070811</v>
+        <v>135070815</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1878,13 +1874,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>834975</v>
+        <v>835010</v>
       </c>
       <c r="R12" t="n">
-        <v>7294913</v>
+        <v>7294999</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135070815</v>
+        <v>135070816</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1980,7 +1976,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1994,13 +1990,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835010</v>
+        <v>835002</v>
       </c>
       <c r="R13" t="n">
-        <v>7294999</v>
+        <v>7295005</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,7 +2062,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135070816</v>
+        <v>135070819</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -2096,7 +2092,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835002</v>
+        <v>834991</v>
       </c>
       <c r="R14" t="n">
-        <v>7295005</v>
+        <v>7295085</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2145,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2151,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135070819</v>
+        <v>135070820</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2212,7 +2213,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2226,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>834991</v>
+        <v>835029</v>
       </c>
       <c r="R15" t="n">
-        <v>7295085</v>
+        <v>7295077</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2261,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,12 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal grov gran</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2299,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135070820</v>
+        <v>135070821</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2331,11 +2327,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>bålar</t>
@@ -2347,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835029</v>
+        <v>835033</v>
       </c>
       <c r="R16" t="n">
-        <v>7295077</v>
+        <v>7295094</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,50 +2411,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135070821</v>
+        <v>135070804</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835033</v>
+        <v>834905</v>
       </c>
       <c r="R17" t="n">
-        <v>7295094</v>
+        <v>7294914</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2494,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2491,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födohack efter hästmyror i tallstambas</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2523,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135070804</v>
+        <v>135070817</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2566,13 +2558,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834905</v>
+        <v>834961</v>
       </c>
       <c r="R18" t="n">
-        <v>7294914</v>
+        <v>7295090</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,12 +2603,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födohack efter hästmyror i tallstambas</t>
+          <t>Födohack efter hästmyror i granbas</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,48 +2635,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135070817</v>
+        <v>134939124</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>834961</v>
+        <v>834938</v>
       </c>
       <c r="R19" t="n">
-        <v>7295090</v>
+        <v>7295016</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,27 +2716,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födohack efter hästmyror i granbas</t>
+          <t>Tjugotre stjälkar med blomknoppar på ett stort mossbelupet stenblock.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,6 +2735,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2748,14 +2747,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Andersson, AK Gustavsson, Mats Williamson</t>
+          <t>Lars Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134939124</v>
+        <v>134939126</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2785,7 +2784,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2806,10 +2805,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>834938</v>
+        <v>834984</v>
       </c>
       <c r="R20" t="n">
-        <v>7295016</v>
+        <v>7295031</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,11 +2841,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tjugotre stjälkar med blomknoppar på ett stort mossbelupet stenblock.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,7 +2868,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134939126</v>
+        <v>134939127</v>
       </c>
       <c r="B21" t="n">
         <v>99195</v>
@@ -2904,7 +2898,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2925,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834984</v>
+        <v>834947</v>
       </c>
       <c r="R21" t="n">
-        <v>7295031</v>
+        <v>7295068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,6 +2955,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bladskott täckande nära en kvarts kvadratmeter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,7 +2987,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134939127</v>
+        <v>134939128</v>
       </c>
       <c r="B22" t="n">
         <v>99195</v>
@@ -3018,7 +3017,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3028,7 +3027,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3039,10 +3038,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834947</v>
+        <v>835002</v>
       </c>
       <c r="R22" t="n">
-        <v>7295068</v>
+        <v>7295086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3078,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bladskott täckande nära en kvarts kvadratmeter.</t>
+          <t>Även en fjolårsstjälk med torr frukt.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,7 +3106,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134939128</v>
+        <v>135070795</v>
       </c>
       <c r="B23" t="n">
         <v>99195</v>
@@ -3137,7 +3136,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3145,11 +3144,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3158,13 +3153,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>835002</v>
+        <v>834938</v>
       </c>
       <c r="R23" t="n">
-        <v>7295086</v>
+        <v>7295010</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3188,17 +3183,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Även en fjolårsstjälk med torr frukt.</t>
+          <t>Stjälkar med blomknoppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,14 +3224,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Andersson</t>
+          <t>Lars Andersson, AK Gustavsson, Mats Williamson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135070795</v>
+        <v>135070796</v>
       </c>
       <c r="B24" t="n">
         <v>99195</v>
@@ -3256,7 +3261,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3264,19 +3269,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sagoskogen, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834938</v>
+        <v>834931</v>
       </c>
       <c r="R24" t="n">
-        <v>7295010</v>
+        <v>7295005</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3308,7 +3310,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,12 +3320,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stjälkar med blomknoppar</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,7 +3329,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3351,7 +3347,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135070796</v>
+        <v>135070799</v>
       </c>
       <c r="B25" t="n">
         <v>99195</v>
@@ -3381,7 +3377,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3395,10 +3391,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834931</v>
+        <v>834919</v>
       </c>
       <c r="R25" t="n">
-        <v>7295005</v>
+        <v>7294971</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3430,7 +3426,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,7 +3436,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,7 +3463,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135070799</v>
+        <v>135070800</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3497,12 +3493,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3511,10 +3507,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>834919</v>
+        <v>834937</v>
       </c>
       <c r="R26" t="n">
-        <v>7294971</v>
+        <v>7294978</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3546,7 +3542,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3556,7 +3552,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,7 +3579,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135070800</v>
+        <v>135070801</v>
       </c>
       <c r="B27" t="n">
         <v>99195</v>
@@ -3613,12 +3609,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3627,10 +3623,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>834937</v>
+        <v>834901</v>
       </c>
       <c r="R27" t="n">
-        <v>7294978</v>
+        <v>7294947</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3662,7 +3658,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3672,7 +3668,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3699,7 +3695,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135070801</v>
+        <v>135070806</v>
       </c>
       <c r="B28" t="n">
         <v>99195</v>
@@ -3729,7 +3725,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3743,13 +3739,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>834901</v>
+        <v>834948</v>
       </c>
       <c r="R28" t="n">
-        <v>7294947</v>
+        <v>7294878</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3778,7 +3774,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3788,7 +3784,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3815,7 +3811,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135070806</v>
+        <v>135070812</v>
       </c>
       <c r="B29" t="n">
         <v>99195</v>
@@ -3845,7 +3841,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3859,13 +3855,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>834948</v>
+        <v>834994</v>
       </c>
       <c r="R29" t="n">
-        <v>7294878</v>
+        <v>7294936</v>
       </c>
       <c r="S29" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3894,7 +3890,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3904,7 +3900,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3931,7 +3927,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135070812</v>
+        <v>135070814</v>
       </c>
       <c r="B30" t="n">
         <v>99195</v>
@@ -3961,12 +3957,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3975,13 +3971,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>834994</v>
+        <v>835001</v>
       </c>
       <c r="R30" t="n">
-        <v>7294936</v>
+        <v>7294945</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4010,7 +4006,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4020,7 +4016,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4047,7 +4043,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135070814</v>
+        <v>135070818</v>
       </c>
       <c r="B31" t="n">
         <v>99195</v>
@@ -4077,12 +4073,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4091,13 +4087,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>835001</v>
+        <v>834972</v>
       </c>
       <c r="R31" t="n">
-        <v>7294945</v>
+        <v>7295100</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4126,7 +4122,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +4132,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,122 +4156,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>135070818</v>
-      </c>
-      <c r="B32" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sagoskogen, Nb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>834972</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7295100</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Nederluleå</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Lars Andersson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Lars Andersson, AK Gustavsson, Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60732-2025 artfynd.xlsx
+++ b/artfynd/A 60732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939129</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939131</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070802</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070808</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070810</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070811</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070815</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070816</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070819</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070820</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070821</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2520,6 +2600,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070804</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2632,6 +2717,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070817</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2751,6 +2841,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939124</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2865,6 +2960,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939126</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2984,6 +3084,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939127</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3103,6 +3208,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134939128</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3228,6 +3338,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070795</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3344,6 +3459,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070796</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3460,6 +3580,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070799</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3576,6 +3701,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070800</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3692,6 +3822,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070801</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3808,6 +3943,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070806</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3924,6 +4064,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070812</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4040,6 +4185,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070814</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4156,8 +4306,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135070818</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 60732-2025 artfynd.xlsx
+++ b/artfynd/A 60732-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135070805</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>134939129</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>134939130</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>134939131</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135070797</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135070802</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135070803</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135070808</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>135070810</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135070811</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>135070815</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135070816</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>135070819</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135070820</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135070821</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>135070804</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>135070817</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>134939124</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>134939126</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>134939127</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>134939128</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135070795</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135070796</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135070799</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135070800</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135070801</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>135070806</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135070812</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135070814</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>135070818</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 60732-2025 artfynd.xlsx
+++ b/artfynd/A 60732-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135070805</v>
       </c>
       <c r="B2" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>134939129</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>134939130</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>134939131</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135070797</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135070802</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135070803</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>135070808</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>135070810</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135070811</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>135070815</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135070816</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>135070819</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135070820</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135070821</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>134939124</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>134939127</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>134939128</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135070795</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135070796</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135070799</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135070800</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135070801</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>135070806</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135070812</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135070814</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>135070818</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
